--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_4_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_4_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268900.2608276921</v>
+        <v>255599.0086376057</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928679</v>
+        <v>5095622.684065036</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284261</v>
+        <v>22414251.77131046</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4042949.682958145</v>
+        <v>3987555.939167324</v>
       </c>
     </row>
     <row r="11">
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2119,25 +2119,25 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>23.28271064538745</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="21">
@@ -2153,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2195,22 +2195,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S21" t="n">
-        <v>35.23199999999998</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2235,25 +2235,25 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H22" t="n">
-        <v>26.86753361060322</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2308,28 +2308,28 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.361305680129117</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="24">
@@ -2387,25 +2387,25 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>23.55470292302859</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H24" t="n">
-        <v>34.48540867374211</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0.7465913262578567</v>
@@ -2466,19 +2466,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="F25" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2505,16 +2505,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>19.72731862540288</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2542,31 +2542,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>12.35200489467393</v>
       </c>
     </row>
     <row r="27">
@@ -2624,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2639,10 +2639,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2678,19 +2678,19 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="28">
@@ -2718,16 +2718,16 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I28" t="n">
-        <v>24.1460928754967</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2788,10 +2788,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2833,22 +2833,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="Y29" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="30">
@@ -2861,28 +2861,28 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>34.48540867374211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="31">
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>22.4487593605094</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2955,16 +2955,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>26.86753361060322</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="32">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>13.29201143084264</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3028,19 +3028,19 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3067,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3216,19 +3216,19 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R34" t="n">
-        <v>9.137025436486075</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>19.72731862540289</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3319,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y35" t="n">
-        <v>35.23199999999998</v>
+        <v>2.361305680129117</v>
       </c>
     </row>
     <row r="36">
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3389,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3420,25 +3420,25 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H37" t="n">
-        <v>26.86753361060322</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="I37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3553,13 +3553,13 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="39">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3617,16 +3617,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -3663,19 +3663,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.1792675346265591</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3696,22 +3696,22 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3739,19 +3739,19 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2.361305680129117</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3818,19 +3818,19 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>34.48540867374211</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3854,22 +3854,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="W42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3930,19 +3930,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T43" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="E20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="F20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H20" t="n">
-        <v>15.26998924708335</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I20" t="n">
-        <v>15.26998924708335</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K20" t="n">
-        <v>42.8</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L20" t="n">
-        <v>42.8</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M20" t="n">
-        <v>80.80000000000001</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N20" t="n">
-        <v>120.4</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O20" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S20" t="n">
-        <v>136.4821104592046</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T20" t="n">
-        <v>96.07807005516418</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U20" t="n">
-        <v>55.67402965112376</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V20" t="n">
-        <v>15.26998924708335</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W20" t="n">
-        <v>15.26998924708335</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="X20" t="n">
-        <v>15.26998924708335</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.26998924708335</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>43.60404040404041</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="C21" t="n">
-        <v>43.60404040404041</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="D21" t="n">
-        <v>43.60404040404041</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K21" t="n">
-        <v>42.8</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L21" t="n">
-        <v>80.80000000000001</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M21" t="n">
-        <v>80.80000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N21" t="n">
-        <v>80.80000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O21" t="n">
-        <v>120.4</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="P21" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R21" t="n">
-        <v>119.5959595959596</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S21" t="n">
-        <v>84.00808080808082</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T21" t="n">
-        <v>84.00808080808082</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="U21" t="n">
-        <v>84.00808080808082</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="V21" t="n">
-        <v>84.00808080808082</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="W21" t="n">
-        <v>43.60404040404041</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="X21" t="n">
-        <v>43.60404040404041</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="Y21" t="n">
-        <v>43.60404040404041</v>
+        <v>26.7539638887914</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>160</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="D22" t="n">
-        <v>160</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="E22" t="n">
-        <v>160</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="F22" t="n">
-        <v>160</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="G22" t="n">
-        <v>160</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H22" t="n">
-        <v>132.8610771610068</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I22" t="n">
-        <v>92.45703675696643</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J22" t="n">
-        <v>52.05299635292603</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K22" t="n">
-        <v>29.55856016516557</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L22" t="n">
-        <v>56.87268517287855</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M22" t="n">
-        <v>96.06072336510073</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N22" t="n">
-        <v>135.6607233651007</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="U22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="V22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="W22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="X22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Y22" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84.00808080808082</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="C23" t="n">
-        <v>43.60404040404041</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="D23" t="n">
-        <v>43.60404040404041</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K23" t="n">
-        <v>42.8</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L23" t="n">
-        <v>82.40000000000001</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M23" t="n">
-        <v>120.4</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N23" t="n">
-        <v>120.4</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O23" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q23" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R23" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S23" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T23" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="U23" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="V23" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="W23" t="n">
-        <v>124.4121212121212</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="X23" t="n">
-        <v>124.4121212121212</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="Y23" t="n">
-        <v>84.00808080808082</v>
+        <v>72.39977328887976</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C24" t="n">
-        <v>119.5959595959596</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D24" t="n">
-        <v>79.19191919191917</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E24" t="n">
-        <v>79.19191919191917</v>
+        <v>86.56747182608416</v>
       </c>
       <c r="F24" t="n">
-        <v>79.19191919191917</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="G24" t="n">
-        <v>79.19191919191917</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="H24" t="n">
-        <v>44.35817305682612</v>
+        <v>2.961334673611005</v>
       </c>
       <c r="I24" t="n">
-        <v>3.954132652785714</v>
+        <v>2.961334673611005</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K24" t="n">
-        <v>42.8</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="L24" t="n">
-        <v>80.80000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M24" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N24" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O24" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y24" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="C25" t="n">
-        <v>93.23739943079403</v>
+        <v>59.81587415154178</v>
       </c>
       <c r="D25" t="n">
-        <v>93.23739943079403</v>
+        <v>31.94716176738407</v>
       </c>
       <c r="E25" t="n">
-        <v>52.83335902675362</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="F25" t="n">
-        <v>43.60404040404041</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="L25" t="n">
-        <v>30.51412500771298</v>
+        <v>31.39257439093933</v>
       </c>
       <c r="M25" t="n">
-        <v>69.70216319993516</v>
+        <v>58.7066993986523</v>
       </c>
       <c r="N25" t="n">
-        <v>109.3021631999352</v>
+        <v>86.02082440636528</v>
       </c>
       <c r="O25" t="n">
-        <v>133.6414398348344</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P25" t="n">
-        <v>133.6414398348344</v>
+        <v>107.6111710058034</v>
       </c>
       <c r="Q25" t="n">
-        <v>133.6414398348344</v>
+        <v>107.6111710058034</v>
       </c>
       <c r="R25" t="n">
-        <v>93.23739943079403</v>
+        <v>107.6111710058034</v>
       </c>
       <c r="S25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="T25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="U25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="V25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="W25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="X25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
       <c r="Y25" t="n">
-        <v>93.23739943079403</v>
+        <v>87.68458653569951</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84.00808080808082</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="C26" t="n">
-        <v>84.00808080808082</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="D26" t="n">
-        <v>84.00808080808082</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="E26" t="n">
-        <v>84.00808080808082</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="F26" t="n">
-        <v>84.00808080808082</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="G26" t="n">
-        <v>43.60404040404041</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="H26" t="n">
-        <v>43.60404040404041</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K26" t="n">
-        <v>41.20000000000001</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="L26" t="n">
-        <v>80.80000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M26" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N26" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O26" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q26" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X26" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y26" t="n">
-        <v>84.00808080808082</v>
+        <v>97.8833284203818</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>43.60404040404041</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="C27" t="n">
-        <v>3.2</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="D27" t="n">
-        <v>3.2</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K27" t="n">
-        <v>3.2</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L27" t="n">
-        <v>42.8</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M27" t="n">
-        <v>80.80000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N27" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O27" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P27" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R27" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T27" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U27" t="n">
-        <v>119.5959595959596</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V27" t="n">
-        <v>79.19191919191917</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W27" t="n">
-        <v>79.19191919191917</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X27" t="n">
-        <v>43.60404040404041</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y27" t="n">
-        <v>43.60404040404041</v>
+        <v>82.49138865710684</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="E28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="F28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H28" t="n">
-        <v>76.44298915645805</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I28" t="n">
-        <v>52.05299635292603</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J28" t="n">
-        <v>52.05299635292603</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K28" t="n">
-        <v>29.55856016516557</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L28" t="n">
-        <v>56.87268517287855</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M28" t="n">
-        <v>96.06072336510073</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N28" t="n">
-        <v>135.6607233651007</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O28" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P28" t="n">
-        <v>157.2510699645389</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q28" t="n">
-        <v>157.2510699645389</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R28" t="n">
-        <v>157.2510699645389</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="S28" t="n">
-        <v>157.2510699645389</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T28" t="n">
-        <v>157.2510699645389</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="U28" t="n">
-        <v>116.8470295604985</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="V28" t="n">
-        <v>116.8470295604985</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="W28" t="n">
-        <v>116.8470295604985</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="X28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y28" t="n">
-        <v>116.8470295604985</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>84.00808080808082</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C29" t="n">
-        <v>84.00808080808082</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D29" t="n">
-        <v>84.00808080808082</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E29" t="n">
-        <v>43.60404040404041</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K29" t="n">
-        <v>42.8</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L29" t="n">
-        <v>82.40000000000001</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="M29" t="n">
-        <v>120.4</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N29" t="n">
-        <v>120.4</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q29" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R29" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S29" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T29" t="n">
-        <v>124.4121212121212</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="U29" t="n">
-        <v>124.4121212121212</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="V29" t="n">
-        <v>124.4121212121212</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="W29" t="n">
-        <v>124.4121212121212</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="X29" t="n">
-        <v>124.4121212121212</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y29" t="n">
-        <v>84.00808080808082</v>
+        <v>30.07591440498301</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.5959595959596</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="C30" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="D30" t="n">
-        <v>79.19191919191917</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E30" t="n">
-        <v>79.19191919191917</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F30" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G30" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H30" t="n">
-        <v>3.954132652785714</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I30" t="n">
-        <v>3.954132652785714</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L30" t="n">
-        <v>41.20000000000001</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M30" t="n">
-        <v>41.20000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N30" t="n">
-        <v>80.80000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O30" t="n">
-        <v>120.4</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="P30" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R30" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S30" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T30" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U30" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V30" t="n">
-        <v>160</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="W30" t="n">
-        <v>160</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="X30" t="n">
-        <v>160</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="Y30" t="n">
-        <v>119.5959595959596</v>
+        <v>54.62267627294912</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>160</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="C31" t="n">
-        <v>160</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="D31" t="n">
-        <v>160</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="E31" t="n">
-        <v>160</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="F31" t="n">
-        <v>160</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="G31" t="n">
-        <v>160</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="H31" t="n">
-        <v>132.8610771610068</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="I31" t="n">
-        <v>92.45703675696643</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="J31" t="n">
-        <v>52.05299635292603</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="K31" t="n">
-        <v>29.55856016516557</v>
+        <v>4.078449383226349</v>
       </c>
       <c r="L31" t="n">
-        <v>56.87268517287855</v>
+        <v>31.39257439093933</v>
       </c>
       <c r="M31" t="n">
-        <v>96.06072336510073</v>
+        <v>58.7066993986523</v>
       </c>
       <c r="N31" t="n">
-        <v>135.6607233651007</v>
+        <v>86.02082440636528</v>
       </c>
       <c r="O31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X31" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y31" t="n">
-        <v>160</v>
+        <v>82.49138865710684</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.69626341965168</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="C32" t="n">
-        <v>15.26998924708335</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="D32" t="n">
-        <v>15.26998924708335</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="E32" t="n">
-        <v>15.26998924708335</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="F32" t="n">
-        <v>15.26998924708335</v>
+        <v>44.53106090472204</v>
       </c>
       <c r="G32" t="n">
-        <v>15.26998924708335</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="H32" t="n">
-        <v>15.26998924708335</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="I32" t="n">
-        <v>15.26998924708335</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="L32" t="n">
-        <v>42.8</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M32" t="n">
-        <v>82.40000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N32" t="n">
-        <v>122</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O32" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q32" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R32" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S32" t="n">
-        <v>109.5043442277325</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T32" t="n">
-        <v>69.10030382369209</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="U32" t="n">
-        <v>28.69626341965168</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="V32" t="n">
-        <v>28.69626341965168</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="W32" t="n">
-        <v>28.69626341965168</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="X32" t="n">
-        <v>28.69626341965168</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="Y32" t="n">
-        <v>28.69626341965168</v>
+        <v>100.2684856730375</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F33" t="n">
-        <v>84.00808080808082</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G33" t="n">
-        <v>43.60404040404041</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L33" t="n">
-        <v>42.8</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M33" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N33" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O33" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P33" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R33" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S33" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T33" t="n">
-        <v>119.5959595959596</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="U33" t="n">
-        <v>119.5959595959596</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="V33" t="n">
-        <v>119.5959595959596</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="W33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y33" t="n">
-        <v>119.5959595959596</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F34" t="n">
-        <v>69.96260056920597</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G34" t="n">
-        <v>69.96260056920597</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H34" t="n">
-        <v>69.96260056920597</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I34" t="n">
-        <v>69.96260056920597</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J34" t="n">
-        <v>29.55856016516557</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K34" t="n">
-        <v>29.55856016516557</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L34" t="n">
-        <v>56.87268517287855</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M34" t="n">
-        <v>96.06072336510073</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N34" t="n">
-        <v>135.6607233651007</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O34" t="n">
-        <v>160</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P34" t="n">
-        <v>160</v>
+        <v>105.7399236434024</v>
       </c>
       <c r="Q34" t="n">
-        <v>119.5959595959596</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="R34" t="n">
-        <v>110.3666409732464</v>
+        <v>50.00249887508694</v>
       </c>
       <c r="S34" t="n">
-        <v>110.3666409732464</v>
+        <v>22.13378649092923</v>
       </c>
       <c r="T34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="U34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y34" t="n">
-        <v>110.3666409732464</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84.00808080808082</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="C35" t="n">
-        <v>43.60404040404041</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="D35" t="n">
-        <v>43.60404040404041</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="E35" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="G35" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K35" t="n">
-        <v>3.2</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L35" t="n">
-        <v>3.2</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M35" t="n">
-        <v>41.20000000000001</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="N35" t="n">
-        <v>80.80000000000001</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q35" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R35" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S35" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T35" t="n">
-        <v>160</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="U35" t="n">
-        <v>160</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="V35" t="n">
-        <v>160</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="W35" t="n">
-        <v>160</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="X35" t="n">
-        <v>160</v>
+        <v>44.53106090472204</v>
       </c>
       <c r="Y35" t="n">
-        <v>124.4121212121212</v>
+        <v>42.14590365206637</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.2</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C36" t="n">
-        <v>3.2</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K36" t="n">
-        <v>3.2</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L36" t="n">
-        <v>3.2</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M36" t="n">
-        <v>41.20000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N36" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O36" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P36" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R36" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S36" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T36" t="n">
-        <v>124.4121212121212</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U36" t="n">
-        <v>84.00808080808082</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V36" t="n">
-        <v>84.00808080808082</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W36" t="n">
-        <v>43.60404040404041</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="X36" t="n">
-        <v>3.2</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.2</v>
+        <v>82.49138865710684</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="C37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="D37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="E37" t="n">
-        <v>133.6414398348344</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="F37" t="n">
-        <v>133.6414398348344</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="G37" t="n">
-        <v>133.6414398348344</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="H37" t="n">
-        <v>106.5025169958413</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I37" t="n">
-        <v>66.09847659180087</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J37" t="n">
-        <v>25.69443618776046</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L37" t="n">
-        <v>30.51412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M37" t="n">
-        <v>69.70216319993516</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N37" t="n">
-        <v>109.3021631999352</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="U37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="V37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="W37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="X37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Y37" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>43.60404040404041</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="C38" t="n">
-        <v>3.2</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="D38" t="n">
-        <v>3.2</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="G38" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L38" t="n">
-        <v>41.20000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M38" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N38" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O38" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q38" t="n">
-        <v>149.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R38" t="n">
-        <v>149.9083846317729</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="S38" t="n">
-        <v>149.9083846317729</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="T38" t="n">
-        <v>149.9083846317729</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="U38" t="n">
-        <v>149.9083846317729</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="V38" t="n">
-        <v>149.9083846317729</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="W38" t="n">
-        <v>124.4121212121212</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="X38" t="n">
-        <v>124.4121212121212</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="Y38" t="n">
-        <v>84.00808080808082</v>
+        <v>44.53106090472204</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="C39" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D39" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E39" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F39" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G39" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H39" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L39" t="n">
-        <v>41.20000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M39" t="n">
-        <v>41.20000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N39" t="n">
-        <v>80.80000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O39" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P39" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R39" t="n">
-        <v>160</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="S39" t="n">
-        <v>160</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T39" t="n">
-        <v>160</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U39" t="n">
-        <v>119.5959595959596</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="V39" t="n">
-        <v>119.5959595959596</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="W39" t="n">
-        <v>119.5959595959596</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="X39" t="n">
-        <v>119.5959595959596</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y39" t="n">
-        <v>79.19191919191917</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.2</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="C40" t="n">
-        <v>3.2</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="D40" t="n">
-        <v>3.2</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="E40" t="n">
-        <v>3.2</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="F40" t="n">
-        <v>3.2</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="G40" t="n">
-        <v>3.2</v>
+        <v>80.43906297690118</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>80.43906297690118</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>52.57035059274347</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>24.70163820858575</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L40" t="n">
-        <v>30.51412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M40" t="n">
-        <v>69.70216319993516</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N40" t="n">
-        <v>109.3021631999352</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O40" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P40" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q40" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R40" t="n">
-        <v>93.23739943079403</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S40" t="n">
-        <v>93.23739943079403</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T40" t="n">
-        <v>52.83335902675362</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="U40" t="n">
-        <v>12.42931862271321</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="V40" t="n">
-        <v>12.42931862271321</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="W40" t="n">
-        <v>3.2</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="X40" t="n">
-        <v>3.2</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.2</v>
+        <v>108.4888536788635</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.2</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="C41" t="n">
-        <v>3.2</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="D41" t="n">
-        <v>3.2</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="E41" t="n">
-        <v>3.2</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="F41" t="n">
-        <v>3.2</v>
+        <v>97.8833284203818</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K41" t="n">
-        <v>42.8</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L41" t="n">
-        <v>82.40000000000001</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="M41" t="n">
-        <v>122</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N41" t="n">
-        <v>160</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O41" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="U41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="V41" t="n">
-        <v>160</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="W41" t="n">
-        <v>119.5959595959596</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="X41" t="n">
-        <v>79.19191919191917</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="Y41" t="n">
-        <v>38.78787878787876</v>
+        <v>100.2684856730375</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="C42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="D42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="E42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="F42" t="n">
-        <v>38.78787878787876</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="G42" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H42" t="n">
-        <v>38.78787878787876</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I42" t="n">
-        <v>3.954132652785714</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K42" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L42" t="n">
-        <v>42.8</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M42" t="n">
-        <v>82.40000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N42" t="n">
-        <v>120.4</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O42" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P42" t="n">
-        <v>160</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S42" t="n">
-        <v>119.5959595959596</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="T42" t="n">
-        <v>119.5959595959596</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="U42" t="n">
-        <v>119.5959595959596</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="V42" t="n">
-        <v>119.5959595959596</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="W42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="Y42" t="n">
-        <v>79.19191919191917</v>
+        <v>30.07591440498301</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="D43" t="n">
-        <v>3.2</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6414398348344</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q43" t="n">
-        <v>93.23739943079403</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R43" t="n">
-        <v>52.83335902675362</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S43" t="n">
-        <v>12.42931862271321</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="U43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="V43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="X43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.2</v>
+        <v>52.75142891054807</v>
       </c>
     </row>
     <row r="44">
@@ -9381,22 +9381,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>260.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L20" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M20" t="n">
-        <v>268.7300716111112</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>269.4130635965909</v>
+        <v>255.8883403615407</v>
       </c>
       <c r="O20" t="n">
-        <v>270.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P20" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>177.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>176.9382181637126</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869681</v>
       </c>
       <c r="N21" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q21" t="n">
-        <v>179.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9545,10 +9545,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M22" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9618,19 +9618,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>260.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L23" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
-        <v>268.7300716111111</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O23" t="n">
-        <v>270.0982114216868</v>
+        <v>256.5734881866366</v>
       </c>
       <c r="P23" t="n">
         <v>231.2329957552695</v>
@@ -9697,22 +9697,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>177.841438974359</v>
+        <v>164.3167157393088</v>
       </c>
       <c r="L24" t="n">
-        <v>176.9382181637126</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N24" t="n">
-        <v>171.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O24" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9782,10 +9782,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M25" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,22 +9855,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>258.4736894288189</v>
+        <v>246.5651278099304</v>
       </c>
       <c r="L26" t="n">
-        <v>275.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M26" t="n">
-        <v>270.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N26" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P26" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L27" t="n">
-        <v>178.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>180.5178723058567</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O27" t="n">
-        <v>182.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P27" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10019,10 +10019,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M28" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>268.7300716111111</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N29" t="n">
-        <v>229.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O29" t="n">
-        <v>270.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,22 +10174,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>176.9382181637126</v>
+        <v>165.029656544824</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N30" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>173.9744074143302</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10256,10 +10256,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M31" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10329,19 +10329,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>220.0898510449805</v>
+        <v>246.5651278099304</v>
       </c>
       <c r="L32" t="n">
-        <v>275.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M32" t="n">
-        <v>270.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N32" t="n">
-        <v>269.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O32" t="n">
-        <v>268.4820498055251</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L33" t="n">
-        <v>178.5543797798742</v>
+        <v>165.029656544824</v>
       </c>
       <c r="M33" t="n">
-        <v>180.5178723058567</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>179.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10493,10 +10493,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M34" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>220.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L35" t="n">
-        <v>235.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M35" t="n">
-        <v>268.7300716111112</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N35" t="n">
-        <v>269.4130635965909</v>
+        <v>255.8883403615407</v>
       </c>
       <c r="O35" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M36" t="n">
-        <v>180.5178723058567</v>
+        <v>168.6093106869681</v>
       </c>
       <c r="N36" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>179.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10730,10 +10730,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M37" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10803,22 +10803,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>220.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L38" t="n">
-        <v>274.1502533538256</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M38" t="n">
-        <v>270.3462332272727</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P38" t="n">
-        <v>271.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L39" t="n">
-        <v>176.9382181637126</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869681</v>
       </c>
       <c r="N39" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10967,10 +10967,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M40" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>270.3462332272727</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N41" t="n">
-        <v>267.7969019804293</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11122,22 +11122,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>178.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M42" t="n">
-        <v>182.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N42" t="n">
-        <v>169.7255504671717</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O42" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11204,10 +11204,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M43" t="n">
-        <v>178.5096609094456</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23944,13 +23944,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I20" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23977,25 +23977,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>185.7373589408579</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>324.9396744681266</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>358.6479133957374</v>
       </c>
     </row>
     <row r="21">
@@ -24011,10 +24011,10 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>123.1437713153523</v>
       </c>
       <c r="E21" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
         <v>145.0692123933839</v>
@@ -24053,22 +24053,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>60.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S21" t="n">
-        <v>136.4511711038379</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>198.3513568206587</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>179.8319801819373</v>
+        <v>152.2419549216212</v>
       </c>
       <c r="C22" t="n">
         <v>167.2468210986278</v>
@@ -24093,25 +24093,25 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E22" t="n">
-        <v>146.4339626465692</v>
+        <v>123.9852032860598</v>
       </c>
       <c r="F22" t="n">
-        <v>145.4210480229312</v>
+        <v>117.8310227626151</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9909793584588</v>
+        <v>140.4009540981426</v>
       </c>
       <c r="H22" t="n">
-        <v>135.3596388968363</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J22" t="n">
-        <v>53.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24166,28 +24166,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>404.5147400615823</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24226,13 +24226,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>323.9996679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>346.2379386560536</v>
+        <v>358.6479133957374</v>
       </c>
     </row>
     <row r="24">
@@ -24245,25 +24245,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>107.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>134.0903775323723</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>117.4791871330677</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>109.7534919028945</v>
       </c>
       <c r="H24" t="n">
-        <v>77.75003556275435</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I24" t="n">
-        <v>49.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24324,19 +24324,19 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
-        <v>167.2468210986278</v>
+        <v>139.6567958383117</v>
       </c>
       <c r="D25" t="n">
-        <v>148.6154730182124</v>
+        <v>121.0254477578962</v>
       </c>
       <c r="E25" t="n">
-        <v>106.4339626465692</v>
+        <v>118.843937386253</v>
       </c>
       <c r="F25" t="n">
-        <v>136.2840225864452</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>127.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24363,16 +24363,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
-        <v>224.0165980369723</v>
+        <v>204.2892794115694</v>
       </c>
       <c r="T25" t="n">
         <v>227.9455894282815</v>
@@ -24400,31 +24400,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>355.1438164031645</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>354.683041620683</v>
+        <v>327.0930163603668</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>354.3403448119457</v>
       </c>
       <c r="F26" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>170.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24448,7 +24448,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>114.6371179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>346.2379386560536</v>
+        <v>373.8859337613796</v>
       </c>
     </row>
     <row r="27">
@@ -24482,13 +24482,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>130.0550551950848</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
@@ -24497,10 +24497,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>65.09533860212863</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -24536,19 +24536,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>170.5409852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>178.0926705169882</v>
       </c>
     </row>
     <row r="28">
@@ -24576,16 +24576,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
-        <v>122.2271725074396</v>
+        <v>134.6371472471234</v>
       </c>
       <c r="I28" t="n">
-        <v>131.3043820517616</v>
+        <v>127.8604496669421</v>
       </c>
       <c r="J28" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24600,13 +24600,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>177.2933913771695</v>
+        <v>154.8446320166601</v>
       </c>
       <c r="S28" t="n">
         <v>224.0165980369723</v>
@@ -24615,7 +24615,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24624,7 +24624,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
-        <v>225.7096553890372</v>
+        <v>198.119630128721</v>
       </c>
       <c r="Y28" t="n">
         <v>218.5846533520948</v>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>355.1438164031645</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24646,10 +24646,10 @@
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24691,22 +24691,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>187.8638495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>300.1622332098187</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>355.4205056437274</v>
       </c>
       <c r="Y29" t="n">
-        <v>346.2379386560536</v>
+        <v>358.6479133957374</v>
       </c>
     </row>
     <row r="30">
@@ -24719,28 +24719,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>132.7084989883157</v>
+        <v>148.4072047390293</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>119.8550403043226</v>
       </c>
       <c r="E30" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>105.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>77.75003556275435</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24776,7 +24776,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>205.2105618891091</v>
       </c>
       <c r="W30" t="n">
         <v>251.6949831609196</v>
@@ -24785,7 +24785,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>165.6826957773044</v>
+        <v>178.0926705169882</v>
       </c>
     </row>
     <row r="31">
@@ -24795,13 +24795,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>179.8319801819373</v>
+        <v>152.2419549216212</v>
       </c>
       <c r="C31" t="n">
-        <v>167.2468210986278</v>
+        <v>139.6567958383117</v>
       </c>
       <c r="D31" t="n">
-        <v>148.6154730182124</v>
+        <v>126.166713657703</v>
       </c>
       <c r="E31" t="n">
         <v>146.4339626465692</v>
@@ -24813,16 +24813,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>135.3596388968363</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
-        <v>53.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>190.9946280917787</v>
       </c>
     </row>
     <row r="32">
@@ -24877,7 +24877,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>351.9808803401649</v>
+        <v>337.6828665106914</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
@@ -24886,19 +24886,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>379.2860204813953</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>210.4758895704059</v>
+        <v>196.1652945356643</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24925,13 +24925,13 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>169.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24965,13 +24965,13 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>109.8372123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>97.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25007,16 +25007,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>160.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>198.3513568206587</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>205.2105618891091</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>227.3936889116331</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -25044,7 +25044,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>105.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
         <v>167.9909793584588</v>
@@ -25056,7 +25056,7 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J34" t="n">
-        <v>53.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
         <v>22.26949182588285</v>
@@ -25074,19 +25074,19 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46.16204325169439</v>
+        <v>58.57201799137825</v>
       </c>
       <c r="R34" t="n">
-        <v>168.1563659406834</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S34" t="n">
-        <v>224.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>208.2182708028786</v>
       </c>
       <c r="U34" t="n">
         <v>286.3190293564909</v>
@@ -25111,16 +25111,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>342.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>341.9303700722618</v>
+        <v>354.3403448119457</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
@@ -25135,7 +25135,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25165,7 +25165,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U35" t="n">
         <v>251.3456529078365</v>
@@ -25177,10 +25177,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>342.1410754181529</v>
       </c>
       <c r="Y35" t="n">
-        <v>351.0059386560536</v>
+        <v>383.8766329759245</v>
       </c>
     </row>
     <row r="36">
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>142.2318894005809</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>145.1184737279996</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>119.8550403043226</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
@@ -25238,7 +25238,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>64.92583415264315</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
         <v>171.6831711038378</v>
@@ -25247,16 +25247,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>211.6949831609196</v>
+        <v>224.1049579006035</v>
       </c>
       <c r="X36" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25278,25 +25278,25 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
-        <v>146.4339626465692</v>
+        <v>118.843937386253</v>
       </c>
       <c r="F37" t="n">
-        <v>145.4210480229312</v>
+        <v>117.8310227626151</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>140.4009540981426</v>
       </c>
       <c r="H37" t="n">
-        <v>135.3596388968363</v>
+        <v>139.7784131469302</v>
       </c>
       <c r="I37" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J37" t="n">
-        <v>53.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25348,10 +25348,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>342.7338416634806</v>
+        <v>355.1438164031645</v>
       </c>
       <c r="C38" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
@@ -25363,7 +25363,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>400.9921424803934</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25396,7 +25396,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>122.2790926808335</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
@@ -25411,13 +25411,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>323.9996679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>346.2379386560536</v>
+        <v>358.6479133957374</v>
       </c>
     </row>
     <row r="39">
@@ -25427,10 +25427,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>138.9431583895512</v>
       </c>
       <c r="C39" t="n">
-        <v>132.7084989883157</v>
+        <v>145.1184737279996</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
@@ -25448,7 +25448,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>54.16463285141511</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>75.85653990335669</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U39" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25496,7 +25496,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25509,7 +25509,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
-        <v>167.2468210986278</v>
+        <v>139.6567958383117</v>
       </c>
       <c r="D40" t="n">
         <v>148.6154730182124</v>
@@ -25521,19 +25521,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9909793584588</v>
+        <v>167.8117118238322</v>
       </c>
       <c r="H40" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I40" t="n">
-        <v>155.4504749272583</v>
+        <v>127.8604496669421</v>
       </c>
       <c r="J40" t="n">
-        <v>93.35918011667277</v>
+        <v>65.76915485635664</v>
       </c>
       <c r="K40" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25554,22 +25554,22 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>187.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>277.3859729001049</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>347.5018416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
         <v>365.2728917710076</v>
@@ -25597,19 +25597,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>404.5147400615823</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25648,13 +25648,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>309.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>329.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25676,19 +25676,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>105.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>109.7534919028945</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>54.91122417767296</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,22 +25712,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S42" t="n">
-        <v>131.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>198.3513568206587</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>208.4992929001388</v>
       </c>
       <c r="W42" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -25749,13 +25749,13 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D43" t="n">
-        <v>148.6154730182124</v>
+        <v>121.0254477578962</v>
       </c>
       <c r="E43" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F43" t="n">
-        <v>145.4210480229312</v>
+        <v>122.9722886624218</v>
       </c>
       <c r="G43" t="n">
         <v>167.9909793584588</v>
@@ -25788,19 +25788,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>46.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
-        <v>184.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T43" t="n">
-        <v>218.8085639917954</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>258.7290040961748</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586833</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586833</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586833</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586833</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367475.9709332837</v>
+        <v>357465.9437586834</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586833</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586833</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367475.9709332836</v>
+        <v>357465.9437586834</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>64504.44331886784</v>
+      </c>
+      <c r="C2" t="n">
         <v>64504.44331886783</v>
-      </c>
-      <c r="C2" t="n">
-        <v>64504.44331886784</v>
       </c>
       <c r="D2" t="n">
         <v>64504.44331886782</v>
       </c>
       <c r="E2" t="n">
+        <v>64504.44331886783</v>
+      </c>
+      <c r="F2" t="n">
         <v>64504.44331886782</v>
       </c>
-      <c r="F2" t="n">
-        <v>64504.44331886784</v>
-      </c>
       <c r="G2" t="n">
-        <v>64504.44331886784</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="H2" t="n">
-        <v>71115.72110201053</v>
+        <v>69180.83107499292</v>
       </c>
       <c r="I2" t="n">
-        <v>71115.72110201052</v>
+        <v>69180.83107499292</v>
       </c>
       <c r="J2" t="n">
-        <v>71115.72110201053</v>
+        <v>69180.83107499294</v>
       </c>
       <c r="K2" t="n">
-        <v>71115.72110201053</v>
+        <v>69180.83107499292</v>
       </c>
       <c r="L2" t="n">
-        <v>71115.72110201052</v>
+        <v>69180.83107499294</v>
       </c>
       <c r="M2" t="n">
-        <v>71115.72110201053</v>
+        <v>69180.83107499291</v>
       </c>
       <c r="N2" t="n">
-        <v>71115.72110201052</v>
+        <v>69180.83107499292</v>
       </c>
       <c r="O2" t="n">
-        <v>71115.72110201053</v>
+        <v>69180.83107499292</v>
       </c>
       <c r="P2" t="n">
-        <v>64504.44331886783</v>
+        <v>64504.44331886782</v>
       </c>
     </row>
     <row r="3">
@@ -26331,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>7444.037125460638</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="C4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="D4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="E4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="F4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="G4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="H4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="I4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="J4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="K4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="L4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="M4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="N4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="O4" t="n">
-        <v>23783.71317440812</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="P4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
     </row>
     <row r="5">
@@ -26435,28 +26435,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.362212578555</v>
+        <v>7841.065392608441</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.36221257857</v>
+        <v>7841.065392608434</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.36221257854</v>
+        <v>7841.065392608427</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257854</v>
+        <v>41468.66539260843</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257857</v>
+        <v>41468.66539260843</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257855</v>
+        <v>41468.66539260843</v>
       </c>
       <c r="H6" t="n">
-        <v>34107.6479276024</v>
+        <v>35295.74941410207</v>
       </c>
       <c r="I6" t="n">
-        <v>44900.00792760239</v>
+        <v>42739.78653956271</v>
       </c>
       <c r="J6" t="n">
-        <v>44900.0079276024</v>
+        <v>42739.78653956272</v>
       </c>
       <c r="K6" t="n">
-        <v>44900.0079276024</v>
+        <v>42739.78653956271</v>
       </c>
       <c r="L6" t="n">
-        <v>44900.0079276024</v>
+        <v>42739.78653956272</v>
       </c>
       <c r="M6" t="n">
-        <v>44900.00792760241</v>
+        <v>42739.78653956269</v>
       </c>
       <c r="N6" t="n">
-        <v>44900.00792760239</v>
+        <v>42739.78653956271</v>
       </c>
       <c r="O6" t="n">
-        <v>44900.0079276024</v>
+        <v>42739.78653956271</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257855</v>
+        <v>41468.66539260842</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
   </sheetData>
@@ -36036,22 +36036,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="O20" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36200,10 +36200,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M22" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36273,19 +36273,19 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O23" t="n">
-        <v>40</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36352,22 +36352,22 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>40</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="L24" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36437,10 +36437,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M25" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,22 +36510,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M26" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36674,10 +36674,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M28" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36747,22 +36747,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,22 +36829,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36911,10 +36911,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M31" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36984,19 +36984,19 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M32" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O32" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M33" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37148,10 +37148,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M34" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M35" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N35" t="n">
-        <v>40</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M36" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37385,10 +37385,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M37" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37458,22 +37458,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L38" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M38" t="n">
-        <v>40</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L39" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37622,10 +37622,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M40" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N41" t="n">
-        <v>38.38383838383839</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M42" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N42" t="n">
-        <v>38.38383838383839</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37859,10 +37859,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M43" t="n">
-        <v>39.58387696184059</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
